--- a/data/trans_camb/P43C-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P43C-Edad-trans_camb.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,9 +515,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -529,25 +526,18 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -578,21 +568,6 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023/2007</t>
         </is>
@@ -607,9 +582,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -624,17 +596,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12,57</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16,12</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-10,23</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -648,21 +620,6 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-10,23</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,57</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>16,12</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>-10,23</t>
         </is>
@@ -677,47 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,29; 19,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,02; 22,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-16,72; -1,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,16; 18,58</t>
+          <t>6,29; 19,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,77; 22,38</t>
+          <t>9,02; 22,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,52; -2,45</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,16; 18,58</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9,77; 22,38</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>-16,52; -2,45</t>
+          <t>-16,72; -1,96</t>
         </is>
       </c>
     </row>
@@ -730,17 +672,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-38,47%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -754,21 +696,6 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-38,47%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>47,26%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>60,59%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>-38,47%</t>
         </is>
@@ -783,47 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,4; 82,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>31,96; 96,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-59,39; -7,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,43; 77,53</t>
+          <t>20,4; 82,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,88; 93,19</t>
+          <t>31,96; 96,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-58,95; -8,68</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20,43; 77,53</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>31,88; 93,19</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>-58,95; -8,68</t>
+          <t>-59,39; -7,69</t>
         </is>
       </c>
     </row>
@@ -840,17 +752,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11,74</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4,63</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,89</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -864,21 +776,6 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-0,89</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11,74</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>4,63</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>-0,89</t>
         </is>
@@ -893,47 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,31; 17,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,29; 10,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-12,09; 17,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,34; 17,55</t>
+          <t>6,31; 17,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 10,37</t>
+          <t>-0,29; 10,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 16,64</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>6,34; 17,55</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-0,61; 10,37</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>-10,88; 16,64</t>
+          <t>-12,09; 17,28</t>
         </is>
       </c>
     </row>
@@ -946,17 +828,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-1,42%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -970,21 +852,6 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-1,42%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,68%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7,36%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>-1,42%</t>
         </is>
@@ -999,47 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,54; 28,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,23; 18,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-18,85; 28,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,72; 29,35</t>
+          <t>9,54; 28,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 17,69</t>
+          <t>-0,23; 18,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,3; 27,97</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9,72; 29,35</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-0,79; 17,69</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>-17,3; 27,97</t>
+          <t>-18,85; 28,19</t>
         </is>
       </c>
     </row>
@@ -1056,17 +908,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,81</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,18</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2,51</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1080,21 +932,6 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-2,51</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,81</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>7,18</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>-2,51</t>
         </is>
@@ -1109,47 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,73; 14,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,95; 12,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,95; 2,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,1; 14,26</t>
+          <t>4,73; 14,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 11,8</t>
+          <t>2,95; 12,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 2,23</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,1; 14,26</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2,62; 11,8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>-7,7; 2,23</t>
+          <t>-7,95; 2,47</t>
         </is>
       </c>
     </row>
@@ -1162,17 +984,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-3,51%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1186,21 +1008,6 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-3,51%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>13,68%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>-3,51%</t>
         </is>
@@ -1215,47 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,34; 21,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,01; 17,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,71; 3,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,91; 20,61</t>
+          <t>6,34; 21,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,6; 17,03</t>
+          <t>4,01; 17,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 3,25</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>6,91; 20,61</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>3,6; 17,03</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>-10,43; 3,25</t>
+          <t>-10,71; 3,54</t>
         </is>
       </c>
     </row>
@@ -1272,17 +1064,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,57</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4,3</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,25</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1296,21 +1088,6 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,25</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,57</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4,3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>5,25</t>
         </is>
@@ -1325,47 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,81; 12,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,36; 9,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,18; 11,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,5; 12,64</t>
+          <t>2,81; 12,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 9,52</t>
+          <t>-1,36; 9,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 11,72</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2,5; 12,64</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-0,77; 9,52</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>-0,1; 11,72</t>
+          <t>0,18; 11,38</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1140,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1402,21 +1164,6 @@
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,47%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>5,95%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>7,26%</t>
         </is>
@@ -1431,47 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,77; 18,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,71; 13,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,24; 16,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,12; 18,03</t>
+          <t>3,77; 18,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 13,73</t>
+          <t>-1,71; 13,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 17,07</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,12; 18,03</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-1,03; 13,73</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>-0,15; 17,07</t>
+          <t>0,24; 16,3</t>
         </is>
       </c>
     </row>
@@ -1488,17 +1220,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15,18</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,85</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14,6</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1512,21 +1244,6 @@
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>14,6</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>15,18</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>10,85</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>14,6</t>
         </is>
@@ -1541,47 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,63; 22,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,66; 17,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,5; 20,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,68; 22,99</t>
+          <t>8,63; 22,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,57; 18,24</t>
+          <t>4,66; 17,35</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,73; 21,13</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>8,68; 22,99</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>4,57; 18,24</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>8,73; 21,13</t>
+          <t>8,5; 20,61</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1296,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1618,21 +1320,6 @@
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>25,82%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>26,84%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>19,19%</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>25,82%</t>
         </is>
@@ -1647,47 +1334,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,06; 43,0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,93; 33,5</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,88; 39,19</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14,71; 43,5</t>
+          <t>14,06; 43,0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7,86; 35,41</t>
+          <t>7,93; 33,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,43; 40,98</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>14,71; 43,5</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>7,86; 35,41</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>14,43; 40,98</t>
+          <t>13,88; 39,19</t>
         </is>
       </c>
     </row>
@@ -1704,17 +1376,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12,7</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19,13</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,95</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1728,21 +1400,6 @@
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-0,95</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>12,7</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>19,13</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>-0,95</t>
         </is>
@@ -1757,47 +1414,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,49; 20,52</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,02; 25,58</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-26,38; 25,44</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,05; 20,02</t>
+          <t>5,49; 20,52</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>11,9; 26,48</t>
+          <t>12,02; 25,58</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-27,08; 25,44</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>5,05; 20,02</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>11,9; 26,48</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>-27,08; 25,44</t>
+          <t>-26,38; 25,44</t>
         </is>
       </c>
     </row>
@@ -1810,17 +1452,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-2,44%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1834,21 +1476,6 @@
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-2,44%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>32,68%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>49,22%</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>-2,44%</t>
         </is>
@@ -1863,47 +1490,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,2; 57,31</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>27,89; 72,23</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-62,01; 67,43</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12,14; 56,87</t>
+          <t>12,2; 57,31</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>28,34; 77,16</t>
+          <t>27,89; 72,23</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-63,98; 67,28</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>12,14; 56,87</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>28,34; 77,16</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>-63,98; 67,28</t>
+          <t>-62,01; 67,43</t>
         </is>
       </c>
     </row>
@@ -1920,17 +1532,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,0</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15,1</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23,84</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1944,21 +1556,6 @@
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>23,84</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>9,0</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>15,1</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>23,84</t>
         </is>
@@ -1973,47 +1570,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,41; 16,26</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,37; 22,16</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,41; 29,62</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,39; 16,54</t>
+          <t>2,41; 16,26</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,49; 21,93</t>
+          <t>7,37; 22,16</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,59; 29,39</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>2,39; 16,54</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>7,49; 21,93</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>17,59; 29,39</t>
+          <t>17,41; 29,62</t>
         </is>
       </c>
     </row>
@@ -2026,17 +1608,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>118,14%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2050,21 +1632,6 @@
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>118,14%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>44,58%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>74,86%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>118,14%</t>
         </is>
@@ -2079,47 +1646,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,86; 94,37</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>30,8; 129,57</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>70,96; 183,63</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9,59; 99,39</t>
+          <t>9,86; 94,37</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>32,1; 131,32</t>
+          <t>30,8; 129,57</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>74,29; 185,28</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>9,59; 99,39</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>32,1; 131,32</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>74,29; 185,28</t>
+          <t>70,96; 183,63</t>
         </is>
       </c>
     </row>
@@ -2136,17 +1688,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11,29</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,13</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,16</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2160,21 +1712,6 @@
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>2,16</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>11,29</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>10,13</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>2,16</t>
         </is>
@@ -2189,47 +1726,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,89; 13,51</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,82; 12,42</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-12,99; 7,8</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>8,86; 13,63</t>
+          <t>8,89; 13,51</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>7,95; 12,56</t>
+          <t>7,82; 12,42</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 7,85</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>8,86; 13,63</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>7,95; 12,56</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>-10,19; 7,85</t>
+          <t>-12,99; 7,8</t>
         </is>
       </c>
     </row>
@@ -2242,17 +1764,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2266,21 +1788,6 @@
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>4,01%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>20,97%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>18,82%</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>4,01%</t>
         </is>
@@ -2295,47 +1802,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,14; 25,63</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,23; 23,63</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-23,65; 14,55</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16,13; 26,12</t>
+          <t>16,14; 25,63</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>14,45; 23,75</t>
+          <t>14,23; 23,63</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 14,66</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>16,13; 26,12</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>14,45; 23,75</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>-18,72; 14,66</t>
+          <t>-23,65; 14,55</t>
         </is>
       </c>
     </row>
@@ -2347,14 +1839,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>

--- a/data/trans_camb/P43C-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P43C-Edad-trans_camb.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-10,23</t>
+          <t>-10,74</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-10,23</t>
+          <t>-10,74</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,29; 19,29</t>
+          <t>6,24; 18,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,02; 22,38</t>
+          <t>9,61; 22,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,72; -1,96</t>
+          <t>-16,8; -3,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,29; 19,29</t>
+          <t>6,24; 18,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,02; 22,38</t>
+          <t>9,61; 22,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,72; -1,96</t>
+          <t>-16,8; -3,55</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-38,47%</t>
+          <t>-40,4%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-38,47%</t>
+          <t>-40,4%</t>
         </is>
       </c>
     </row>
@@ -710,32 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,4; 82,14</t>
+          <t>21,08; 79,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,96; 96,13</t>
+          <t>32,5; 91,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-59,39; -7,69</t>
+          <t>-58,77; -13,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,4; 82,14</t>
+          <t>21,08; 79,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,96; 96,13</t>
+          <t>32,5; 91,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,39; -7,69</t>
+          <t>-58,77; -13,25</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,89</t>
+          <t>-10,84</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,89</t>
+          <t>-10,84</t>
         </is>
       </c>
     </row>
@@ -790,32 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,31; 17,1</t>
+          <t>6,59; 17,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 10,76</t>
+          <t>-1,12; 10,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 17,28</t>
+          <t>-17,88; -4,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,31; 17,1</t>
+          <t>6,59; 17,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 10,76</t>
+          <t>-1,12; 10,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 17,28</t>
+          <t>-17,88; -4,12</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-1,42%</t>
+          <t>-17,24%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-1,42%</t>
+          <t>-17,24%</t>
         </is>
       </c>
     </row>
@@ -866,32 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,54; 28,41</t>
+          <t>10,28; 29,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 18,04</t>
+          <t>-1,71; 18,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,85; 28,19</t>
+          <t>-27,72; -6,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,54; 28,41</t>
+          <t>10,28; 29,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 18,04</t>
+          <t>-1,71; 18,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,85; 28,19</t>
+          <t>-27,72; -6,59</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,51</t>
+          <t>-3,24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,51</t>
+          <t>-3,24</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,73; 14,77</t>
+          <t>5,68; 14,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,95; 12,13</t>
+          <t>2,52; 11,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 2,47</t>
+          <t>-8,27; 1,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,73; 14,77</t>
+          <t>5,68; 14,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,95; 12,13</t>
+          <t>2,52; 11,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 2,47</t>
+          <t>-8,27; 1,98</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-3,51%</t>
+          <t>-4,52%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-3,51%</t>
+          <t>-4,52%</t>
         </is>
       </c>
     </row>
@@ -1022,32 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,34; 21,4</t>
+          <t>7,68; 20,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,01; 17,68</t>
+          <t>3,42; 17,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 3,54</t>
+          <t>-11,07; 2,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,34; 21,4</t>
+          <t>7,68; 20,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,01; 17,68</t>
+          <t>3,42; 17,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 3,54</t>
+          <t>-11,07; 2,9</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>2,81</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>2,81</t>
         </is>
       </c>
     </row>
@@ -1102,32 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,81; 12,92</t>
+          <t>2,34; 12,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 9,04</t>
+          <t>-1,0; 9,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 11,38</t>
+          <t>-2,18; 8,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,81; 12,92</t>
+          <t>2,34; 12,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 9,04</t>
+          <t>-1,0; 9,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 11,38</t>
+          <t>-2,18; 8,14</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -1178,32 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,77; 18,83</t>
+          <t>3,15; 18,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 13,13</t>
+          <t>-1,35; 13,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,24; 16,3</t>
+          <t>-2,85; 11,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,77; 18,83</t>
+          <t>3,15; 18,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 13,13</t>
+          <t>-1,35; 13,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,24; 16,3</t>
+          <t>-2,85; 11,71</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14,6</t>
+          <t>14,09</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,6</t>
+          <t>14,09</t>
         </is>
       </c>
     </row>
@@ -1258,32 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,63; 22,25</t>
+          <t>8,24; 21,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,66; 17,35</t>
+          <t>3,49; 17,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,5; 20,61</t>
+          <t>8,67; 19,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,63; 22,25</t>
+          <t>8,24; 21,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,66; 17,35</t>
+          <t>3,49; 17,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,5; 20,61</t>
+          <t>8,67; 19,94</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -1334,32 +1334,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>14,06; 43,0</t>
+          <t>13,44; 39,94</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7,93; 33,5</t>
+          <t>5,68; 33,6</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13,88; 39,19</t>
+          <t>14,23; 37,77</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14,06; 43,0</t>
+          <t>13,44; 39,94</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7,93; 33,5</t>
+          <t>5,68; 33,6</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,88; 39,19</t>
+          <t>14,23; 37,77</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,95</t>
+          <t>23,61</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0,95</t>
+          <t>23,61</t>
         </is>
       </c>
     </row>
@@ -1414,32 +1414,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>5,49; 20,52</t>
+          <t>5,23; 19,87</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>12,02; 25,58</t>
+          <t>12,15; 25,98</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-26,38; 25,44</t>
+          <t>17,47; 30,22</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,49; 20,52</t>
+          <t>5,23; 19,87</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,02; 25,58</t>
+          <t>12,15; 25,98</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-26,38; 25,44</t>
+          <t>17,47; 30,22</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-2,44%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-2,44%</t>
+          <t>60,76%</t>
         </is>
       </c>
     </row>
@@ -1490,32 +1490,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>12,2; 57,31</t>
+          <t>11,78; 54,93</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>27,89; 72,23</t>
+          <t>28,74; 75,16</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-62,01; 67,43</t>
+          <t>40,35; 88,51</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12,2; 57,31</t>
+          <t>11,78; 54,93</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>27,89; 72,23</t>
+          <t>28,74; 75,16</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-62,01; 67,43</t>
+          <t>40,35; 88,51</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23,84</t>
+          <t>23,7</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,84</t>
+          <t>23,7</t>
         </is>
       </c>
     </row>
@@ -1570,32 +1570,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,41; 16,26</t>
+          <t>1,85; 15,59</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>7,37; 22,16</t>
+          <t>7,39; 22,34</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17,41; 29,62</t>
+          <t>16,91; 29,4</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,41; 16,26</t>
+          <t>1,85; 15,59</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,37; 22,16</t>
+          <t>7,39; 22,34</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,41; 29,62</t>
+          <t>16,91; 29,4</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>118,14%</t>
+          <t>117,46%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>118,14%</t>
+          <t>117,46%</t>
         </is>
       </c>
     </row>
@@ -1646,32 +1646,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>9,86; 94,37</t>
+          <t>7,73; 92,57</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>30,8; 129,57</t>
+          <t>30,96; 137,78</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>70,96; 183,63</t>
+          <t>69,57; 187,19</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9,86; 94,37</t>
+          <t>7,73; 92,57</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>30,8; 129,57</t>
+          <t>30,96; 137,78</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>70,96; 183,63</t>
+          <t>69,57; 187,19</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>4,13</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>4,13</t>
         </is>
       </c>
     </row>
@@ -1726,32 +1726,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>8,89; 13,51</t>
+          <t>8,68; 13,54</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>7,82; 12,42</t>
+          <t>7,75; 12,68</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 7,8</t>
+          <t>1,49; 6,45</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>8,89; 13,51</t>
+          <t>8,68; 13,54</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>7,82; 12,42</t>
+          <t>7,75; 12,68</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 7,8</t>
+          <t>1,49; 6,45</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -1802,32 +1802,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>16,14; 25,63</t>
+          <t>15,8; 25,81</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>14,23; 23,63</t>
+          <t>14,21; 24,24</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-23,65; 14,55</t>
+          <t>2,77; 12,26</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16,14; 25,63</t>
+          <t>15,8; 25,81</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>14,23; 23,63</t>
+          <t>14,21; 24,24</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-23,65; 14,55</t>
+          <t>2,77; 12,26</t>
         </is>
       </c>
     </row>
